--- a/资源/DataTables/Protagonist.xlsx
+++ b/资源/DataTables/Protagonist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22300" windowHeight="11700"/>
+    <workbookView windowWidth="23230" windowHeight="11710"/>
   </bookViews>
   <sheets>
     <sheet name="Protagonist" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>#</t>
   </si>
@@ -74,6 +74,42 @@
     <t>AttackSpeed</t>
   </si>
   <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>阵容</t>
+  </si>
+  <si>
+    <t>预制体路径</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
+    <t>可视范围</t>
+  </si>
+  <si>
+    <t>攻击类型</t>
+  </si>
+  <si>
+    <t>子弹预制体Id</t>
+  </si>
+  <si>
+    <t>子弹移动速度</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -86,7 +122,7 @@
     <t>陈 良</t>
   </si>
   <si>
-    <t>Entity/Unit/Protagonist/ProtagonistEntity</t>
+    <t>Prefabs/Entity/Unit/Protagonist/ProtagonistEntity</t>
   </si>
   <si>
     <t>3</t>
@@ -114,14 +150,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,153 +606,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1070,8 +1103,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col min="6" max="6" width="11.9090909090909" customWidth="1"/>
     <col min="8" max="8" width="12.4545454545455" customWidth="1"/>
@@ -1128,50 +1161,97 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2">
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2">
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3">
         <v>10</v>
       </c>
-      <c r="O2">
+      <c r="O3">
         <v>0.2</v>
       </c>
     </row>
